--- a/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
+++ b/2025/Factures ventes enregistrées VC CONVENTION EDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E036E519-9BDC-490B-ADFD-A9C99E0AE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C9E6349-73D9-4F3E-BD3A-FB39A631A305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
